--- a/artfynd/A 33874-2023 artfynd.xlsx
+++ b/artfynd/A 33874-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33874-2023 artfynd.xlsx
+++ b/artfynd/A 33874-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126242926</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>565809</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6956787</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126242930</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565790</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6956703</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>nb</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33874-2023 artfynd.xlsx
+++ b/artfynd/A 33874-2023 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>126242930</v>
       </c>
       <c r="B4" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33874-2023 artfynd.xlsx
+++ b/artfynd/A 33874-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126242926</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126242930</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33874-2023 artfynd.xlsx
+++ b/artfynd/A 33874-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126242926</v>
       </c>
       <c r="B3" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126242930</v>
       </c>
       <c r="B4" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
